--- a/artfynd/A 30530-2024 artfynd.xlsx
+++ b/artfynd/A 30530-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>118676814</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
